--- a/templates/XP INFRA90 - template.xlsx
+++ b/templates/XP INFRA90 - template.xlsx
@@ -1,12 +1,12 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr codeName="ThisWorkbook"/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="20355" yWindow="-11640" windowWidth="20730" windowHeight="11040" tabRatio="711" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Email" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Email" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
     <definedName name="DataAnálise">Email!$A$1</definedName>
@@ -1402,14 +1402,14 @@
     <row r="21" ht="15.95" customFormat="1" customHeight="1" s="29">
       <c r="B21" s="30" t="inlineStr">
         <is>
-          <t>2026-03-26</t>
+          <t>2026-04-10</t>
         </is>
       </c>
       <c r="C21" s="31" t="n">
-        <v>1.043339</v>
+        <v>1.03163437</v>
       </c>
       <c r="D21" s="32" t="n">
-        <v>-0.0003305215115120275</v>
+        <v>0.000459666613645382</v>
       </c>
       <c r="E21" s="32" t="n">
         <v>0.0005426623598601132</v>
@@ -1418,23 +1418,23 @@
         <v>0.0005821700069987834</v>
       </c>
       <c r="G21" s="33" t="n">
-        <v>-0.6090739582476825</v>
+        <v>0.8470582219188266</v>
       </c>
       <c r="H21" s="33" t="n">
-        <v>-0.5677405354768099</v>
+        <v>0.7895745368523297</v>
       </c>
     </row>
     <row r="22" ht="15.95" customFormat="1" customHeight="1" s="29">
       <c r="B22" s="34" t="inlineStr">
         <is>
-          <t>2026-03-25</t>
+          <t>2026-04-09</t>
         </is>
       </c>
       <c r="C22" s="35" t="n">
-        <v>1.04368396</v>
+        <v>1.03116038</v>
       </c>
       <c r="D22" s="36" t="n">
-        <v>-0.00239424282112588</v>
+        <v>-1.642782445998581e-05</v>
       </c>
       <c r="E22" s="36" t="n">
         <v>0.0005426623598601132</v>
@@ -1443,23 +1443,23 @@
         <v>0.0005821700069987834</v>
       </c>
       <c r="G22" s="37" t="n">
-        <v>-4.412030386155887</v>
+        <v>-0.03027264405111965</v>
       </c>
       <c r="H22" s="37" t="n">
-        <v>-4.112617950671725</v>
+        <v>-0.02821825972223289</v>
       </c>
     </row>
     <row r="23" ht="15.95" customFormat="1" customHeight="1" s="29">
       <c r="B23" s="34" t="inlineStr">
         <is>
-          <t>2026-03-24</t>
+          <t>2026-04-08</t>
         </is>
       </c>
       <c r="C23" s="35" t="n">
-        <v>1.04618879</v>
+        <v>1.03117732</v>
       </c>
       <c r="D23" s="36" t="n">
-        <v>0.0002419364692518577</v>
+        <v>0.000717850344012172</v>
       </c>
       <c r="E23" s="36" t="n">
         <v>0.0005426623598601132</v>
@@ -1468,23 +1468,23 @@
         <v>0.0005821700069987834</v>
       </c>
       <c r="G23" s="37" t="n">
-        <v>0.4458324128362686</v>
+        <v>1.322830542728666</v>
       </c>
       <c r="H23" s="37" t="n">
-        <v>0.4155770073059833</v>
+        <v>1.23305964818224</v>
       </c>
     </row>
     <row r="24" ht="15.95" customFormat="1" customHeight="1" s="29">
       <c r="B24" s="34" t="inlineStr">
         <is>
-          <t>2026-03-23</t>
+          <t>2026-04-07</t>
         </is>
       </c>
       <c r="C24" s="35" t="n">
-        <v>1.04593574</v>
+        <v>1.03043762</v>
       </c>
       <c r="D24" s="36" t="n">
-        <v>2.214334203731738e-05</v>
+        <v>-0.00090249650111629</v>
       </c>
       <c r="E24" s="36" t="n">
         <v>0.0005426623598601132</v>
@@ -1493,23 +1493,23 @@
         <v>0.0005821700069987834</v>
       </c>
       <c r="G24" s="37" t="n">
-        <v>0.04080500818782689</v>
+        <v>-1.663090289418515</v>
       </c>
       <c r="H24" s="37" t="n">
-        <v>0.03803586885465169</v>
+        <v>-1.55022843888654</v>
       </c>
     </row>
     <row r="25" ht="15.95" customFormat="1" customHeight="1" s="29">
       <c r="B25" s="34" t="inlineStr">
         <is>
-          <t>2026-03-20</t>
+          <t>2026-04-06</t>
         </is>
       </c>
       <c r="C25" s="35" t="n">
-        <v>1.04591258</v>
+        <v>1.031368426396184</v>
       </c>
       <c r="D25" s="36" t="n">
-        <v>0.001493997734404395</v>
+        <v>0.0008552504043539688</v>
       </c>
       <c r="E25" s="36" t="n">
         <v>0.0005426623598601132</v>
@@ -1518,10 +1518,10 @@
         <v>0.0005821700069987834</v>
       </c>
       <c r="G25" s="37" t="n">
-        <v>2.753088927688878</v>
+        <v>1.576026766578088</v>
       </c>
       <c r="H25" s="37" t="n">
-        <v>2.566256791733892</v>
+        <v>1.469073284559911</v>
       </c>
     </row>
     <row r="26" ht="15.95" customHeight="1">
@@ -1573,24 +1573,24 @@
     <row r="28" ht="15.95" customFormat="1" customHeight="1" s="29">
       <c r="B28" s="38" t="inlineStr">
         <is>
-          <t>Mar-26</t>
+          <t>Apr-26</t>
         </is>
       </c>
       <c r="C28" s="38" t="inlineStr"/>
       <c r="D28" s="32" t="n">
-        <v>-0.002076112614765147</v>
+        <v>0.0007804951610241861</v>
       </c>
       <c r="E28" s="32" t="n">
-        <v>0.01048336746569301</v>
+        <v>0.003804826246388782</v>
       </c>
       <c r="F28" s="32" t="n">
-        <v>0.01124174012968759</v>
+        <v>0.004082314319127534</v>
       </c>
       <c r="G28" s="33" t="n">
-        <v>-0.1980387143309876</v>
+        <v>0.2051329313040158</v>
       </c>
       <c r="H28" s="33" t="n">
-        <v>-0.1846789367851044</v>
+        <v>0.1911893842586311</v>
       </c>
       <c r="I28" s="39" t="n"/>
     </row>
@@ -1602,19 +1602,19 @@
       </c>
       <c r="C29" s="40" t="inlineStr"/>
       <c r="D29" s="36" t="n">
-        <v>-0.0009029852678946737</v>
+        <v>-6.810699683224009e-06</v>
       </c>
       <c r="E29" s="36" t="n">
-        <v>0.01159785506263344</v>
+        <v>0.0115104208368324</v>
       </c>
       <c r="F29" s="36" t="n">
-        <v>0.01243701403980046</v>
+        <v>0.01234950728397388</v>
       </c>
       <c r="G29" s="37" t="n">
-        <v>-0.07785795416636627</v>
+        <v>-0.0005916985816391985</v>
       </c>
       <c r="H29" s="37" t="n">
-        <v>-0.07260466740690122</v>
+        <v>-0.0005514956610505702</v>
       </c>
       <c r="I29" s="41" t="n"/>
       <c r="J29" s="42" t="n"/>
@@ -1627,19 +1627,19 @@
       </c>
       <c r="C30" s="40" t="inlineStr"/>
       <c r="D30" s="36" t="n">
-        <v>0.02547261007669288</v>
+        <v>0.02334866228647869</v>
       </c>
       <c r="E30" s="36" t="n">
-        <v>0.03528813776398843</v>
+        <v>0.03519865594435645</v>
       </c>
       <c r="F30" s="36" t="n">
-        <v>0.03786670851308371</v>
+        <v>0.03777700382293214</v>
       </c>
       <c r="G30" s="37" t="n">
-        <v>0.7218462545985552</v>
+        <v>0.6633395980627574</v>
       </c>
       <c r="H30" s="37" t="n">
-        <v>0.6726914241276497</v>
+        <v>0.6180654875627042</v>
       </c>
       <c r="I30" s="41" t="n"/>
     </row>
@@ -1651,19 +1651,19 @@
       </c>
       <c r="C31" s="40" t="inlineStr"/>
       <c r="D31" s="36" t="n">
-        <v>0.06289634249448239</v>
+        <v>0.05406892287935072</v>
       </c>
       <c r="E31" s="36" t="n">
-        <v>0.07186785093087189</v>
+        <v>0.07177520746070365</v>
       </c>
       <c r="F31" s="36" t="n">
-        <v>0.07721385841335238</v>
+        <v>0.07712075287811992</v>
       </c>
       <c r="G31" s="37" t="n">
-        <v>0.8751665964657968</v>
+        <v>0.7533091828254628</v>
       </c>
       <c r="H31" s="37" t="n">
-        <v>0.8145732357755859</v>
+        <v>0.7010943340348369</v>
       </c>
       <c r="I31" s="41" t="n"/>
     </row>
@@ -1676,19 +1676,19 @@
       </c>
       <c r="C32" s="40" t="inlineStr"/>
       <c r="D32" s="36" t="n">
-        <v>0.1544875725976329</v>
+        <v>0.1508900128773145</v>
       </c>
       <c r="E32" s="36" t="n">
-        <v>0.1478169439809287</v>
+        <v>0.148016036262707</v>
       </c>
       <c r="F32" s="36" t="n">
-        <v>0.1592951134207572</v>
+        <v>0.1594961966253503</v>
       </c>
       <c r="G32" s="37" t="n">
-        <v>1.045127631765712</v>
+        <v>1.019416657054014</v>
       </c>
       <c r="H32" s="37" t="n">
-        <v>0.9698199102289735</v>
+        <v>0.9460414484475054</v>
       </c>
       <c r="I32" s="41" t="n"/>
     </row>
@@ -1696,24 +1696,24 @@
       <c r="A33" s="51" t="n"/>
       <c r="B33" s="40" t="inlineStr">
         <is>
-          <t>Ano 2026</t>
+          <t>Últimos 720 dias</t>
         </is>
       </c>
       <c r="C33" s="40" t="inlineStr"/>
       <c r="D33" s="36" t="n">
-        <v>0.0232120546746537</v>
+        <v>0.2980343252943936</v>
       </c>
       <c r="E33" s="36" t="n">
-        <v>0.03243902489712824</v>
+        <v>0.2779304689804314</v>
       </c>
       <c r="F33" s="36" t="n">
-        <v>0.03480618036515426</v>
+        <v>0.3036168714069436</v>
       </c>
       <c r="G33" s="37" t="n">
-        <v>0.715559569014931</v>
+        <v>1.072334121507843</v>
       </c>
       <c r="H33" s="37" t="n">
-        <v>0.6668946270787053</v>
+        <v>0.9816131887313085</v>
       </c>
       <c r="I33" s="41" t="n"/>
     </row>
@@ -1721,24 +1721,24 @@
       <c r="A34" s="51" t="n"/>
       <c r="B34" s="40" t="inlineStr">
         <is>
-          <t>Ano 2025</t>
+          <t>Ano 2026</t>
         </is>
       </c>
       <c r="C34" s="40" t="inlineStr"/>
       <c r="D34" s="36" t="n">
-        <v>0.1643204461145897</v>
+        <v>0.02478044702973148</v>
       </c>
       <c r="E34" s="36" t="n">
-        <v>0.143132751155109</v>
+        <v>0.0380553842733744</v>
       </c>
       <c r="F34" s="36" t="n">
-        <v>0.1545640786666771</v>
+        <v>0.04084631843637321</v>
       </c>
       <c r="G34" s="37" t="n">
-        <v>1.14802827996033</v>
+        <v>0.6511679622446807</v>
       </c>
       <c r="H34" s="37" t="n">
-        <v>1.063121829677856</v>
+        <v>0.6066751662902563</v>
       </c>
       <c r="I34" s="41" t="n"/>
     </row>
@@ -1746,24 +1746,24 @@
       <c r="A35" s="46" t="n"/>
       <c r="B35" s="40" t="inlineStr">
         <is>
-          <t>Ano 2024</t>
+          <t>Ano 2025</t>
         </is>
       </c>
       <c r="C35" s="40" t="inlineStr"/>
       <c r="D35" s="36" t="n">
-        <v>0.1480564386065841</v>
+        <v>0.1643204461145893</v>
       </c>
       <c r="E35" s="36" t="n">
-        <v>0.1092049264357533</v>
+        <v>0.143132751155109</v>
       </c>
       <c r="F35" s="36" t="n">
-        <v>0.1203854500312833</v>
+        <v>0.1545640786666771</v>
       </c>
       <c r="G35" s="37" t="n">
-        <v>1.355767028456245</v>
+        <v>1.148028279960327</v>
       </c>
       <c r="H35" s="37" t="n">
-        <v>1.229853263563913</v>
+        <v>1.063121829677853</v>
       </c>
       <c r="I35" s="41" t="n"/>
     </row>
@@ -1771,29 +1771,50 @@
       <c r="A36" s="46" t="n"/>
       <c r="B36" s="40" t="inlineStr">
         <is>
-          <t>Acumulado²</t>
+          <t>Ano 2024</t>
         </is>
       </c>
       <c r="C36" s="40" t="inlineStr"/>
       <c r="D36" s="36" t="n">
-        <v>0.429234076301072</v>
+        <v>0.1480564386065844</v>
       </c>
       <c r="E36" s="36" t="n">
-        <v>0.3462532860848027</v>
+        <v>0.1092049264357533</v>
       </c>
       <c r="F36" s="36" t="n">
-        <v>0.3798900061942962</v>
+        <v>0.1203854500312833</v>
       </c>
       <c r="G36" s="37" t="n">
-        <v>1.239653437385562</v>
+        <v>1.355767028456247</v>
       </c>
       <c r="H36" s="37" t="n">
-        <v>1.129890413809777</v>
+        <v>1.229853263563915</v>
       </c>
       <c r="I36" s="41" t="n"/>
     </row>
     <row r="37" ht="15.95" customFormat="1" customHeight="1" s="45">
       <c r="A37" s="43" t="n"/>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>Acumulado²</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr"/>
+      <c r="D37" t="n">
+        <v>0.4314248243367758</v>
+      </c>
+      <c r="E37" t="n">
+        <v>0.3535767619354546</v>
+      </c>
+      <c r="F37" t="n">
+        <v>0.387944390018683</v>
+      </c>
+      <c r="G37" t="n">
+        <v>1.220173016957297</v>
+      </c>
+      <c r="H37" t="n">
+        <v>1.112079038740575</v>
+      </c>
       <c r="I37" s="44" t="n"/>
     </row>
     <row r="38" ht="26.1" customHeight="1">
@@ -1819,7 +1840,7 @@
       <c r="C39" s="11" t="n"/>
       <c r="D39" s="11" t="n"/>
       <c r="E39" s="47" t="n">
-        <v>552381039.39</v>
+        <v>546819403.04</v>
       </c>
       <c r="F39" s="47" t="n"/>
       <c r="G39" s="26" t="n"/>
@@ -1835,7 +1856,7 @@
       <c r="C40" s="11" t="n"/>
       <c r="D40" s="11" t="n"/>
       <c r="E40" s="47" t="n">
-        <v>493957630.9626587</v>
+        <v>497094307.5634127</v>
       </c>
       <c r="F40" s="47" t="n"/>
       <c r="G40" s="26" t="n"/>
@@ -1861,7 +1882,7 @@
       </c>
       <c r="C42" s="23" t="inlineStr">
         <is>
-          <t>2026-03-26</t>
+          <t>2026-04-10</t>
         </is>
       </c>
       <c r="D42" s="16" t="n"/>
